--- a/Risk_Rating_Rationale.xlsx
+++ b/Risk_Rating_Rationale.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ratings'!$A$1:$H$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ratings'!$A$1:$H$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="8" min="1" max="1"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Availability model poisoning</t>
+          <t>Integrity data poisoning (targeted, backdoor)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" s="13">
@@ -802,12 +802,12 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Requires model control (supply chain or insider).</t>
+          <t>Requires access to the protected training data.</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Weakens or destabilizes the model; the effect is noticeable and can be reverted by retraining.</t>
+          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process; the effect persists across updates. A backdoor trigger implanted through runtime data has the same effect.</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Availability model poisoning</t>
+          <t>Integrity data poisoning (targeted, backdoor)</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" s="16">
@@ -843,12 +843,12 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>Requires model control (supply chain or insider).</t>
+          <t>Runtime data enter retraining, but the attacker must inject the target pattern over a sustained period without triggering alerts.</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>Weakens or destabilizes the model; the effect is noticeable and can be reverted by retraining.</t>
+          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process; the effect persists across updates. A backdoor trigger implanted through runtime data has the same effect.</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Availability model poisoning</t>
+          <t>Integrity data poisoning (targeted, backdoor)</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" s="16">
@@ -884,12 +884,12 @@
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>Requires model control (supply chain or insider).</t>
+          <t>As in R; operator review adds an obstacle but does not prevent sustained injection of unflagged data.</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>Weakens or destabilizes the model; the effect is noticeable and can be reverted by retraining.</t>
+          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process; the effect persists across updates. A backdoor trigger implanted through runtime data has the same effect.</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Availability model poisoning</t>
+          <t>Integrity data poisoning (targeted, backdoor)</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" s="16">
@@ -925,12 +925,12 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>A single compromised site can submit manipulated updates in every round; model control is obtainable through one participant.</t>
+          <t>Local runtime data enter local training; sustained testing data control at one site is required.</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>Weakens or destabilizes the model; the effect is noticeable and can be reverted by retraining.</t>
+          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process; the effect persists across updates. A backdoor trigger implanted through runtime data has the same effect.</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Targeted data poisoning</t>
+          <t>Availability model poisoning</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F10" s="13">
@@ -966,12 +966,12 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Requires access to the protected training data.</t>
+          <t>Requires model control (supply chain or insider).</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process; the effect persists across updates.</t>
+          <t>Weakens or destabilizes the model; the effect is noticeable and can be reverted by retraining.</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Targeted data poisoning</t>
+          <t>Availability model poisoning</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" s="16">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Runtime data enter retraining, but the attacker must inject the target pattern over a sustained period without triggering alerts.</t>
+          <t>Requires model control (supply chain or insider).</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process; the effect persists across updates.</t>
+          <t>Weakens or destabilizes the model; the effect is noticeable and can be reverted by retraining.</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Targeted data poisoning</t>
+          <t>Availability model poisoning</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F12" s="16">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>As in R; operator review adds an obstacle but does not prevent sustained injection of unflagged data.</t>
+          <t>Requires model control (supply chain or insider).</t>
         </is>
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process; the effect persists across updates.</t>
+          <t>Weakens or destabilizes the model; the effect is noticeable and can be reverted by retraining.</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Targeted data poisoning</t>
+          <t>Availability model poisoning</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" s="16">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>Local runtime data enter local training; sustained testing data control at one site is required.</t>
+          <t>A single compromised site can submit manipulated updates in every round; model control is obtainable through one participant.</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process; the effect persists across updates.</t>
+          <t>Weakens or destabilizes the model; the effect is noticeable and can be reverted by retraining.</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Targeted model poisoning</t>
+          <t>Integrity model poisoning (targeted, backdoor)</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process.</t>
+          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process. A backdoor embedded in updates has the same effect, but must persist across updates.</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Targeted model poisoning</t>
+          <t>Integrity model poisoning (targeted, backdoor)</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process.</t>
+          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process. A backdoor embedded in updates has the same effect, but must persist across updates.</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Targeted model poisoning</t>
+          <t>Integrity model poisoning (targeted, backdoor)</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process.</t>
+          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process. A backdoor embedded in updates has the same effect, but must persist across updates.</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Targeted model poisoning</t>
+          <t>Integrity model poisoning (targeted, backdoor)</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process.</t>
+          <t>Makes a specific attack pattern appear normal, enabling undetected manipulation of the process. A backdoor embedded in updates has the same effect, but must persist across updates.</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Backdoor data poisoning</t>
+          <t>White-box evasion (optimization-based, universal)</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Requires access to the protected training data.</t>
+          <t>Requires white-box knowledge; model internals and anomaly scores are not accessible to the attacker.</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>A trigger suppresses detection whenever the attacker chooses, enabling undetected manipulation of the process.</t>
+          <t>A successful evasion hides an attack on the process.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Backdoor data poisoning</t>
+          <t>White-box evasion (optimization-based, universal)</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>The trigger can be implanted through runtime data, but this requires sustained control and the trigger may be overwritten by later updates.</t>
+          <t>As in S.</t>
         </is>
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>A trigger suppresses detection whenever the attacker chooses, enabling undetected manipulation of the process.</t>
+          <t>A successful evasion hides an attack on the process.</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Backdoor data poisoning</t>
+          <t>White-box evasion (optimization-based, universal)</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>As in R.</t>
+          <t>As in S.</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>A trigger suppresses detection whenever the attacker chooses, enabling undetected manipulation of the process.</t>
+          <t>A successful evasion hides an attack on the process.</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Backdoor data poisoning</t>
+          <t>White-box evasion (optimization-based, universal)</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>As in R, through the local data of one site.</t>
+          <t>Every participating site receives the global model, so a compromised site obtains white-box access.</t>
         </is>
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>A trigger suppresses detection whenever the attacker chooses, enabling undetected manipulation of the process.</t>
+          <t>A successful evasion hides an attack on the process.</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Backdoor model poisoning</t>
+          <t>Physically realizable evasion</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Requires model control.</t>
+          <t>Requires sustained control of field devices and knowledge of the physical constraints of the process, but no model internals.</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>A trigger suppresses detection whenever the attacker chooses, enabling undetected manipulation of the process.</t>
+          <t>A successful evasion hides an attack on the process.</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Backdoor model poisoning</t>
+          <t>Physically realizable evasion</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>Requires model control.</t>
+          <t>Requires sustained control of field devices and knowledge of the physical constraints of the process, but no model internals.</t>
         </is>
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>A trigger suppresses detection whenever the attacker chooses, enabling undetected manipulation of the process.</t>
+          <t>A successful evasion hides an attack on the process.</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Backdoor model poisoning</t>
+          <t>Physically realizable evasion</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>Requires model control.</t>
+          <t>Requires sustained control of field devices and knowledge of the physical constraints of the process, but no model internals.</t>
         </is>
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>A trigger suppresses detection whenever the attacker chooses, enabling undetected manipulation of the process.</t>
+          <t>A successful evasion hides an attack on the process.</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Backdoor model poisoning</t>
+          <t>Physically realizable evasion</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>A compromised site can embed a backdoor in its updates; it must persist across aggregation rounds.</t>
+          <t>Requires sustained control of field devices and knowledge of the physical constraints of the process, but no model internals.</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>A trigger suppresses detection whenever the attacker chooses, enabling undetected manipulation of the process.</t>
+          <t>A successful evasion hides an attack on the process.</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Optimization-based evasion</t>
+          <t>Score-based evasion</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Requires white-box knowledge; model internals and anomaly scores are not accessible to the attacker.</t>
+          <t>Requires observation of anomaly scores, which are visible only to operators under the threat model.</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Optimization-based evasion</t>
+          <t>Score-based evasion</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>As in S.</t>
+          <t>Requires observation of anomaly scores, which are visible only to operators under the threat model.</t>
         </is>
       </c>
       <c r="H27" s="15" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Optimization-based evasion</t>
+          <t>Score-based evasion</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>As in S.</t>
+          <t>Requires observation of anomaly scores, which are visible only to operators under the threat model.</t>
         </is>
       </c>
       <c r="H28" s="15" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Optimization-based evasion</t>
+          <t>Score-based evasion</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>Every participating site receives the global model, so a compromised site obtains white-box access.</t>
+          <t>Requires observation of anomaly scores, which are visible only to operators under the threat model.</t>
         </is>
       </c>
       <c r="H29" s="15" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Universal evasion</t>
+          <t>Decision-based evasion</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Requires white-box knowledge.</t>
+          <t>Requires only indirect query access, i.e., observing whether actions trigger alarms or operator responses, over repeated attempts.</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Universal evasion</t>
+          <t>Decision-based evasion</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Requires white-box knowledge.</t>
+          <t>Requires only indirect query access, i.e., observing whether actions trigger alarms or operator responses, over repeated attempts.</t>
         </is>
       </c>
       <c r="H31" s="15" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Universal evasion</t>
+          <t>Decision-based evasion</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>Requires white-box knowledge.</t>
+          <t>Requires only indirect query access, i.e., observing whether actions trigger alarms or operator responses, over repeated attempts.</t>
         </is>
       </c>
       <c r="H32" s="15" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Universal evasion</t>
+          <t>Decision-based evasion</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>White-box access is obtained through a compromised site that receives the global model.</t>
+          <t>Requires only indirect query access, i.e., observing whether actions trigger alarms or operator responses, over repeated attempts.</t>
         </is>
       </c>
       <c r="H33" s="15" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Physically realizable evasion</t>
+          <t>Training-data inference (reconstruction, membership, property)</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" s="13">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Requires sustained control of field devices and knowledge of the physical constraints of the process, but no model internals.</t>
+          <t>Requires query access to outputs, which are not exposed.</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Leaks partial information about operational data. Rated at the highest impact among the merged subclasses; membership inference alone reveals little.</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Physically realizable evasion</t>
+          <t>Training-data inference (reconstruction, membership, property)</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" s="16">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="G35" s="15" t="inlineStr">
         <is>
-          <t>Requires sustained control of field devices and knowledge of the physical constraints of the process, but no model internals.</t>
+          <t>As in S.</t>
         </is>
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Leaks partial information about operational data. Rated at the highest impact among the merged subclasses; membership inference alone reveals little.</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Physically realizable evasion</t>
+          <t>Training-data inference (reconstruction, membership, property)</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F36" s="16">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>Requires sustained control of field devices and knowledge of the physical constraints of the process, but no model internals.</t>
+          <t>As in S.</t>
         </is>
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Leaks partial information about operational data. Rated at the highest impact among the merged subclasses; membership inference alone reveals little.</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Physically realizable evasion</t>
+          <t>Training-data inference (reconstruction, membership, property)</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F37" s="16">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Requires sustained control of field devices and knowledge of the physical constraints of the process, but no model internals.</t>
+          <t>Exchanged updates can be used to reconstruct local training data of other sites.</t>
         </is>
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Leaks partial information about operational data. Rated at the highest impact among the merged subclasses; membership inference alone reveals little.</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Score-based evasion</t>
+          <t>Model extraction</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F38" s="13">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>Requires observation of anomaly scores, which are visible only to operators under the threat model.</t>
+          <t>Requires extensive query access to outputs, which are not exposed.</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Provides knowledge that enables other attacks; the extraction itself does not affect detection.</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Score-based evasion</t>
+          <t>Model extraction</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F39" s="16">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Requires observation of anomaly scores, which are visible only to operators under the threat model.</t>
+          <t>As in S.</t>
         </is>
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Provides knowledge that enables other attacks; the extraction itself does not affect detection.</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Score-based evasion</t>
+          <t>Model extraction</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F40" s="16">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>Requires observation of anomaly scores, which are visible only to operators under the threat model.</t>
+          <t>As in S.</t>
         </is>
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Provides knowledge that enables other attacks; the extraction itself does not affect detection.</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Score-based evasion</t>
+          <t>Model extraction</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" s="16">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="G41" s="15" t="inlineStr">
         <is>
-          <t>Requires observation of anomaly scores, which are visible only to operators under the threat model.</t>
+          <t>Every participating site receives the global model, so no extraction is needed, but the attacker must first compromise one site (Medium, as for other attacks that require control of a single FL site).</t>
         </is>
       </c>
       <c r="H41" s="15" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Provides knowledge that enables other attacks; the extraction itself does not affect detection.</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Decision-based evasion</t>
+          <t>Gradual poisoning</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F42" s="13">
@@ -2278,14 +2278,10 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>Requires only indirect query access, i.e., observing whether actions trigger alarms or operator responses, over repeated attempts.</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>A successful evasion hides an attack on the process.</t>
-        </is>
-      </c>
+          <t>Not applicable in this mode.</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="n"/>
     </row>
     <row r="43" ht="25.5" customHeight="1" s="9">
       <c r="A43" s="14" t="inlineStr">
@@ -2295,7 +2291,7 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Decision-based evasion</t>
+          <t>Gradual poisoning</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -2319,12 +2315,12 @@
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>Requires only indirect query access, i.e., observing whether actions trigger alarms or operator responses, over repeated attempts.</t>
+          <t>Requires sustained testing data control and knowledge of the adaptation policy.</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Persistently shifts what the detector regards as normal, so that the target attack remains undetected across updates.</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2332,7 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Decision-based evasion</t>
+          <t>Gradual poisoning</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -2360,12 +2356,12 @@
       </c>
       <c r="G44" s="15" t="inlineStr">
         <is>
-          <t>Requires only indirect query access, i.e., observing whether actions trigger alarms or operator responses, over repeated attempts.</t>
+          <t>As in R.</t>
         </is>
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Persistently shifts what the detector regards as normal, so that the target attack remains undetected across updates.</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2373,7 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Decision-based evasion</t>
+          <t>Gradual poisoning</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
@@ -2401,12 +2397,12 @@
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>Requires only indirect query access, i.e., observing whether actions trigger alarms or operator responses, over repeated attempts.</t>
+          <t>As in R, through the local data of one site.</t>
         </is>
       </c>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>A successful evasion hides an attack on the process.</t>
+          <t>Persistently shifts what the detector regards as normal, so that the target attack remains undetected across updates.</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2414,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Data reconstruction</t>
+          <t>Drift masking</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -2428,12 +2424,12 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F46" s="13">
@@ -2442,14 +2438,10 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Requires query access to outputs, which are not exposed.</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>Leaks partial information about operational data.</t>
-        </is>
-      </c>
+          <t>Not applicable in this mode.</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="9">
       <c r="A47" s="14" t="inlineStr">
@@ -2459,7 +2451,7 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Data reconstruction</t>
+          <t>Drift masking</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
@@ -2474,7 +2466,7 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F47" s="16">
@@ -2483,12 +2475,12 @@
       </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>As in S.</t>
+          <t>Retraining is scheduled rather than drift-triggered; the attack depends on legitimate operational changes that the attacker does not control.</t>
         </is>
       </c>
       <c r="H47" s="15" t="inlineStr">
         <is>
-          <t>Leaks partial information about operational data.</t>
+          <t>Adaptation to attack data hides the attack and makes it part of normal behavior.</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2492,7 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Data reconstruction</t>
+          <t>Drift masking</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -2510,12 +2502,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F48" s="16">
@@ -2524,12 +2516,12 @@
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>As in S.</t>
+          <t>Operators decide whether changes are legitimate drift; exploiting this requires sustained control and knowledge of the adaptation policy.</t>
         </is>
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Leaks partial information about operational data.</t>
+          <t>Adaptation to attack data hides the attack and makes it part of normal behavior.</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2533,7 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Data reconstruction</t>
+          <t>Drift masking</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
@@ -2551,12 +2543,12 @@
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F49" s="16">
@@ -2565,12 +2557,12 @@
       </c>
       <c r="G49" s="15" t="inlineStr">
         <is>
-          <t>Exchanged updates can be used to reconstruct local training data of other sites.</t>
+          <t>As in R.</t>
         </is>
       </c>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>Leaks partial information about operational data.</t>
+          <t>Adaptation to attack data hides the attack and makes it part of normal behavior.</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2574,7 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Membership inference</t>
+          <t>Threshold manipulation</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -2592,12 +2584,12 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F50" s="13">
@@ -2606,14 +2598,10 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>Requires query access to outputs, which are not exposed.</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>Knowing whether an operational record was used for training reveals little that is sensitive.</t>
-        </is>
-      </c>
+          <t>Not applicable in this mode.</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="n"/>
     </row>
     <row r="51" ht="25.5" customHeight="1" s="9">
       <c r="A51" s="14" t="inlineStr">
@@ -2623,7 +2611,7 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Membership inference</t>
+          <t>Threshold manipulation</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
@@ -2633,12 +2621,12 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F51" s="16">
@@ -2647,12 +2635,12 @@
       </c>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>As in S.</t>
+          <t>The threshold adapts to recent scores; raising it without triggering alerts requires sustained control of runtime inputs and knowledge of the threshold update rule, since scores are not visible to the attacker.</t>
         </is>
       </c>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>Knowing whether an operational record was used for training reveals little that is sensitive.</t>
+          <t>Can hide an attack by raising the threshold or flood operators with alarms by lowering it.</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2652,7 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Membership inference</t>
+          <t>Threshold manipulation</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -2674,12 +2662,12 @@
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F52" s="16">
@@ -2688,12 +2676,12 @@
       </c>
       <c r="G52" s="15" t="inlineStr">
         <is>
-          <t>As in S.</t>
+          <t>Operator review of alerts and threshold changes requires the manipulation to be slower and more careful.</t>
         </is>
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Knowing whether an operational record was used for training reveals little that is sensitive.</t>
+          <t>Can hide an attack by raising the threshold or flood operators with alarms by lowering it.</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2693,7 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Membership inference</t>
+          <t>Threshold manipulation</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -2720,7 +2708,7 @@
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F53" s="16">
@@ -2729,12 +2717,12 @@
       </c>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>Exchanged updates and the distributed model can be compared across rounds.</t>
+          <t>As in R; thresholds adapt locally at each site.</t>
         </is>
       </c>
       <c r="H53" s="15" t="inlineStr">
         <is>
-          <t>Knowing whether an operational record was used for training reveals little that is sensitive.</t>
+          <t>Can hide an attack by raising the threshold or flood operators with alarms by lowering it.</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2734,7 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>Property inference</t>
+          <t>Feedback poisoning</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -2756,12 +2744,12 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F54" s="13">
@@ -2770,14 +2758,10 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Requires query access to outputs, which are not exposed.</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="inlineStr">
-        <is>
-          <t>Can reveal the operating profile of a plant.</t>
-        </is>
-      </c>
+          <t>Not applicable in this mode.</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="9">
       <c r="A55" s="14" t="inlineStr">
@@ -2787,7 +2771,7 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Property inference</t>
+          <t>Feedback poisoning</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -2797,12 +2781,12 @@
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F55" s="16">
@@ -2811,14 +2795,10 @@
       </c>
       <c r="G55" s="15" t="inlineStr">
         <is>
-          <t>As in S.</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="inlineStr">
-        <is>
-          <t>Can reveal the operating profile of a plant.</t>
-        </is>
-      </c>
+          <t>Not applicable in this mode.</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1" s="9">
       <c r="A56" s="14" t="inlineStr">
@@ -2828,7 +2808,7 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Property inference</t>
+          <t>Feedback poisoning</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -2838,12 +2818,12 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F56" s="16">
@@ -2852,12 +2832,12 @@
       </c>
       <c r="G56" s="15" t="inlineStr">
         <is>
-          <t>As in S.</t>
+          <t>Direct feedback control requires an insider (Low), but the indirect variant only requires generating false alarms through sustained testing data control.</t>
         </is>
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Can reveal the operating profile of a plant.</t>
+          <t>Attack behavior labeled as benign is learned as normal.</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2849,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Property inference</t>
+          <t>Feedback poisoning</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -2879,12 +2859,12 @@
       </c>
       <c r="D57" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F57" s="16">
@@ -2893,14 +2873,10 @@
       </c>
       <c r="G57" s="15" t="inlineStr">
         <is>
-          <t>The global model and updates reveal properties of the operating profiles of other sites.</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="inlineStr">
-        <is>
-          <t>Can reveal the operating profile of a plant.</t>
-        </is>
-      </c>
+          <t>Not applicable in this mode.</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n"/>
     </row>
     <row r="58" ht="25.5" customHeight="1" s="9">
       <c r="A58" s="11" t="inlineStr">
@@ -2910,7 +2886,7 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>Model extraction</t>
+          <t>Adaptation trigger manipulation</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
@@ -2920,12 +2896,12 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F58" s="13">
@@ -2934,14 +2910,10 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>Requires extensive query access to outputs, which are not exposed.</t>
-        </is>
-      </c>
-      <c r="H58" s="12" t="inlineStr">
-        <is>
-          <t>Provides knowledge that enables other attacks; the extraction itself does not affect detection.</t>
-        </is>
-      </c>
+          <t>Not applicable in this mode.</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="n"/>
     </row>
     <row r="59" ht="25.5" customHeight="1" s="9">
       <c r="A59" s="14" t="inlineStr">
@@ -2951,7 +2923,7 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Model extraction</t>
+          <t>Adaptation trigger manipulation</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
@@ -2961,12 +2933,12 @@
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F59" s="16">
@@ -2975,14 +2947,10 @@
       </c>
       <c r="G59" s="15" t="inlineStr">
         <is>
-          <t>As in S.</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="inlineStr">
-        <is>
-          <t>Provides knowledge that enables other attacks; the extraction itself does not affect detection.</t>
-        </is>
-      </c>
+          <t>Not applicable in this mode: updates follow a fixed schedule that the attacker cannot trigger or suppress.</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n"/>
     </row>
     <row r="60" ht="25.5" customHeight="1" s="9">
       <c r="A60" s="14" t="inlineStr">
@@ -2992,7 +2960,7 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Model extraction</t>
+          <t>Adaptation trigger manipulation</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -3002,7 +2970,7 @@
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
@@ -3016,12 +2984,12 @@
       </c>
       <c r="G60" s="15" t="inlineStr">
         <is>
-          <t>As in S.</t>
+          <t>False alarms induced through sustained testing data control initiate feedback-driven updates.</t>
         </is>
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Provides knowledge that enables other attacks; the extraction itself does not affect detection.</t>
+          <t>Causes temporary degradation, resource consumption, or an outdated model.</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3001,7 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Model extraction</t>
+          <t>Adaptation trigger manipulation</t>
         </is>
       </c>
       <c r="C61" s="14" t="inlineStr">
@@ -3043,12 +3011,12 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F61" s="16">
@@ -3057,14 +3025,10 @@
       </c>
       <c r="G61" s="15" t="inlineStr">
         <is>
-          <t>Every participating site receives the global model, so no extraction is needed, but the attacker must first compromise one site (Medium, as for other attacks that require control of a single FL site).</t>
-        </is>
-      </c>
-      <c r="H61" s="15" t="inlineStr">
-        <is>
-          <t>Provides knowledge that enables other attacks; the extraction itself does not affect detection.</t>
-        </is>
-      </c>
+          <t>Not applicable in this mode: aggregation rounds follow a fixed schedule that the attacker cannot trigger or suppress.</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="9">
       <c r="A62" s="11" t="inlineStr">
@@ -3074,7 +3038,7 @@
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>Gradual poisoning</t>
+          <t>Update timing exploitation</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -3111,7 +3075,7 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Gradual poisoning</t>
+          <t>Update timing exploitation</t>
         </is>
       </c>
       <c r="C63" s="14" t="inlineStr">
@@ -3126,7 +3090,7 @@
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F63" s="16">
@@ -3135,12 +3099,12 @@
       </c>
       <c r="G63" s="15" t="inlineStr">
         <is>
-          <t>Requires sustained testing data control and knowledge of the adaptation policy.</t>
+          <t>Requires knowledge of the adaptation schedule and testing data control.</t>
         </is>
       </c>
       <c r="H63" s="15" t="inlineStr">
         <is>
-          <t>Persistently shifts what the detector regards as normal, so that the target attack remains undetected across updates.</t>
+          <t>Exploits a limited window of reduced detection around updates.</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3116,7 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Gradual poisoning</t>
+          <t>Update timing exploitation</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -3167,7 +3131,7 @@
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F64" s="16">
@@ -3176,12 +3140,12 @@
       </c>
       <c r="G64" s="15" t="inlineStr">
         <is>
-          <t>As in R.</t>
+          <t>Requires knowledge of the adaptation schedule and testing data control.</t>
         </is>
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Persistently shifts what the detector regards as normal, so that the target attack remains undetected across updates.</t>
+          <t>Exploits a limited window of reduced detection around updates.</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3157,7 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Gradual poisoning</t>
+          <t>Update timing exploitation</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
@@ -3208,7 +3172,7 @@
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F65" s="16">
@@ -3217,802 +3181,38 @@
       </c>
       <c r="G65" s="15" t="inlineStr">
         <is>
-          <t>As in R, through the local data of one site.</t>
+          <t>Requires knowledge of the adaptation schedule and testing data control.</t>
         </is>
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>Persistently shifts what the detector regards as normal, so that the target attack remains undetected across updates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="9">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>A17</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
-        <is>
-          <t>Drift masking</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F66" s="13">
-        <f>IF(D66="n/a","n/a",CHOOSE(MATCH(D66,{"Low","Medium","High"},0)*MATCH(E66,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G66" s="12" t="inlineStr">
-        <is>
-          <t>Not applicable in this mode.</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="n"/>
-    </row>
-    <row r="67" ht="25.5" customHeight="1" s="9">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>A17</t>
-        </is>
-      </c>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>Drift masking</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D67" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E67" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F67" s="16">
-        <f>IF(D67="n/a","n/a",CHOOSE(MATCH(D67,{"Low","Medium","High"},0)*MATCH(E67,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G67" s="15" t="inlineStr">
-        <is>
-          <t>Retraining is scheduled rather than drift-triggered; the attack depends on legitimate operational changes that the attacker does not control.</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="inlineStr">
-        <is>
-          <t>Adaptation to attack data hides the attack and makes it part of normal behavior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="25.5" customHeight="1" s="9">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>A17</t>
-        </is>
-      </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>Drift masking</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E68" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F68" s="16">
-        <f>IF(D68="n/a","n/a",CHOOSE(MATCH(D68,{"Low","Medium","High"},0)*MATCH(E68,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G68" s="15" t="inlineStr">
-        <is>
-          <t>Operators decide whether changes are legitimate drift; exploiting this requires sustained control and knowledge of the adaptation policy.</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="inlineStr">
-        <is>
-          <t>Adaptation to attack data hides the attack and makes it part of normal behavior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="25.5" customHeight="1" s="9">
-      <c r="A69" s="14" t="inlineStr">
-        <is>
-          <t>A17</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="inlineStr">
-        <is>
-          <t>Drift masking</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E69" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F69" s="16">
-        <f>IF(D69="n/a","n/a",CHOOSE(MATCH(D69,{"Low","Medium","High"},0)*MATCH(E69,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G69" s="15" t="inlineStr">
-        <is>
-          <t>As in R.</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr">
-        <is>
-          <t>Adaptation to attack data hides the attack and makes it part of normal behavior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="9">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>A18</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="inlineStr">
-        <is>
-          <t>Threshold manipulation</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F70" s="13">
-        <f>IF(D70="n/a","n/a",CHOOSE(MATCH(D70,{"Low","Medium","High"},0)*MATCH(E70,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G70" s="12" t="inlineStr">
-        <is>
-          <t>Not applicable in this mode.</t>
-        </is>
-      </c>
-      <c r="H70" s="12" t="n"/>
-    </row>
-    <row r="71" ht="25.5" customHeight="1" s="9">
-      <c r="A71" s="14" t="inlineStr">
-        <is>
-          <t>A18</t>
-        </is>
-      </c>
-      <c r="B71" s="15" t="inlineStr">
-        <is>
-          <t>Threshold manipulation</t>
-        </is>
-      </c>
-      <c r="C71" s="14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D71" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E71" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F71" s="16">
-        <f>IF(D71="n/a","n/a",CHOOSE(MATCH(D71,{"Low","Medium","High"},0)*MATCH(E71,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G71" s="15" t="inlineStr">
-        <is>
-          <t>The threshold adapts to recent scores; raising it without triggering alerts requires sustained control of runtime inputs and knowledge of the threshold update rule, since scores are not visible to the attacker.</t>
-        </is>
-      </c>
-      <c r="H71" s="15" t="inlineStr">
-        <is>
-          <t>Can hide an attack by raising the threshold or flood operators with alarms by lowering it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="25.5" customHeight="1" s="9">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>A18</t>
-        </is>
-      </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>Threshold manipulation</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E72" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F72" s="16">
-        <f>IF(D72="n/a","n/a",CHOOSE(MATCH(D72,{"Low","Medium","High"},0)*MATCH(E72,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G72" s="15" t="inlineStr">
-        <is>
-          <t>Operator review of alerts and threshold changes requires the manipulation to be slower and more careful.</t>
-        </is>
-      </c>
-      <c r="H72" s="15" t="inlineStr">
-        <is>
-          <t>Can hide an attack by raising the threshold or flood operators with alarms by lowering it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="25.5" customHeight="1" s="9">
-      <c r="A73" s="14" t="inlineStr">
-        <is>
-          <t>A18</t>
-        </is>
-      </c>
-      <c r="B73" s="15" t="inlineStr">
-        <is>
-          <t>Threshold manipulation</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E73" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F73" s="16">
-        <f>IF(D73="n/a","n/a",CHOOSE(MATCH(D73,{"Low","Medium","High"},0)*MATCH(E73,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G73" s="15" t="inlineStr">
-        <is>
-          <t>As in R; thresholds adapt locally at each site.</t>
-        </is>
-      </c>
-      <c r="H73" s="15" t="inlineStr">
-        <is>
-          <t>Can hide an attack by raising the threshold or flood operators with alarms by lowering it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="9">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>A19</t>
-        </is>
-      </c>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t>Feedback poisoning</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F74" s="13">
-        <f>IF(D74="n/a","n/a",CHOOSE(MATCH(D74,{"Low","Medium","High"},0)*MATCH(E74,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G74" s="12" t="inlineStr">
-        <is>
-          <t>Not applicable in this mode.</t>
-        </is>
-      </c>
-      <c r="H74" s="12" t="n"/>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="9">
-      <c r="A75" s="14" t="inlineStr">
-        <is>
-          <t>A19</t>
-        </is>
-      </c>
-      <c r="B75" s="15" t="inlineStr">
-        <is>
-          <t>Feedback poisoning</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E75" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F75" s="16">
-        <f>IF(D75="n/a","n/a",CHOOSE(MATCH(D75,{"Low","Medium","High"},0)*MATCH(E75,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G75" s="15" t="inlineStr">
-        <is>
-          <t>Not applicable in this mode.</t>
-        </is>
-      </c>
-      <c r="H75" s="15" t="n"/>
-    </row>
-    <row r="76" ht="38.25" customHeight="1" s="9">
-      <c r="A76" s="14" t="inlineStr">
-        <is>
-          <t>A19</t>
-        </is>
-      </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>Feedback poisoning</t>
-        </is>
-      </c>
-      <c r="C76" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D76" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E76" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F76" s="16">
-        <f>IF(D76="n/a","n/a",CHOOSE(MATCH(D76,{"Low","Medium","High"},0)*MATCH(E76,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G76" s="15" t="inlineStr">
-        <is>
-          <t>Direct feedback control requires an insider (Low), but the indirect variant only requires generating false alarms through sustained testing data control.</t>
-        </is>
-      </c>
-      <c r="H76" s="15" t="inlineStr">
-        <is>
-          <t>Attack behavior labeled as benign is learned as normal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="9">
-      <c r="A77" s="14" t="inlineStr">
-        <is>
-          <t>A19</t>
-        </is>
-      </c>
-      <c r="B77" s="15" t="inlineStr">
-        <is>
-          <t>Feedback poisoning</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="D77" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E77" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F77" s="16">
-        <f>IF(D77="n/a","n/a",CHOOSE(MATCH(D77,{"Low","Medium","High"},0)*MATCH(E77,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G77" s="15" t="inlineStr">
-        <is>
-          <t>Not applicable in this mode.</t>
-        </is>
-      </c>
-      <c r="H77" s="15" t="n"/>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="9">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>A20</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="inlineStr">
-        <is>
-          <t>Adaptation trigger manipulation</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F78" s="13">
-        <f>IF(D78="n/a","n/a",CHOOSE(MATCH(D78,{"Low","Medium","High"},0)*MATCH(E78,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G78" s="12" t="inlineStr">
-        <is>
-          <t>Not applicable in this mode.</t>
-        </is>
-      </c>
-      <c r="H78" s="12" t="n"/>
-    </row>
-    <row r="79" ht="25.5" customHeight="1" s="9">
-      <c r="A79" s="14" t="inlineStr">
-        <is>
-          <t>A20</t>
-        </is>
-      </c>
-      <c r="B79" s="15" t="inlineStr">
-        <is>
-          <t>Adaptation trigger manipulation</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E79" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F79" s="16">
-        <f>IF(D79="n/a","n/a",CHOOSE(MATCH(D79,{"Low","Medium","High"},0)*MATCH(E79,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G79" s="15" t="inlineStr">
-        <is>
-          <t>Not applicable in this mode: updates follow a fixed schedule that the attacker cannot trigger or suppress.</t>
-        </is>
-      </c>
-      <c r="H79" s="15" t="inlineStr"/>
-    </row>
-    <row r="80" ht="25.5" customHeight="1" s="9">
-      <c r="A80" s="14" t="inlineStr">
-        <is>
-          <t>A20</t>
-        </is>
-      </c>
-      <c r="B80" s="15" t="inlineStr">
-        <is>
-          <t>Adaptation trigger manipulation</t>
-        </is>
-      </c>
-      <c r="C80" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D80" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F80" s="16">
-        <f>IF(D80="n/a","n/a",CHOOSE(MATCH(D80,{"Low","Medium","High"},0)*MATCH(E80,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G80" s="15" t="inlineStr">
-        <is>
-          <t>False alarms induced through sustained testing data control initiate feedback-driven updates.</t>
-        </is>
-      </c>
-      <c r="H80" s="15" t="inlineStr">
-        <is>
-          <t>Causes temporary degradation, resource consumption, or an outdated model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="25.5" customHeight="1" s="9">
-      <c r="A81" s="14" t="inlineStr">
-        <is>
-          <t>A20</t>
-        </is>
-      </c>
-      <c r="B81" s="15" t="inlineStr">
-        <is>
-          <t>Adaptation trigger manipulation</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E81" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F81" s="16">
-        <f>IF(D81="n/a","n/a",CHOOSE(MATCH(D81,{"Low","Medium","High"},0)*MATCH(E81,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G81" s="15" t="inlineStr">
-        <is>
-          <t>Not applicable in this mode: aggregation rounds follow a fixed schedule that the attacker cannot trigger or suppress.</t>
-        </is>
-      </c>
-      <c r="H81" s="15" t="inlineStr"/>
-    </row>
-    <row r="82" ht="15" customHeight="1" s="9">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>A21</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>Update timing exploitation</t>
-        </is>
-      </c>
-      <c r="C82" s="11" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F82" s="13">
-        <f>IF(D82="n/a","n/a",CHOOSE(MATCH(D82,{"Low","Medium","High"},0)*MATCH(E82,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G82" s="12" t="inlineStr">
-        <is>
-          <t>Not applicable in this mode.</t>
-        </is>
-      </c>
-      <c r="H82" s="12" t="n"/>
-    </row>
-    <row r="83" ht="25.5" customHeight="1" s="9">
-      <c r="A83" s="14" t="inlineStr">
-        <is>
-          <t>A21</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="inlineStr">
-        <is>
-          <t>Update timing exploitation</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D83" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E83" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F83" s="16">
-        <f>IF(D83="n/a","n/a",CHOOSE(MATCH(D83,{"Low","Medium","High"},0)*MATCH(E83,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G83" s="15" t="inlineStr">
-        <is>
-          <t>Requires knowledge of the adaptation schedule and testing data control.</t>
-        </is>
-      </c>
-      <c r="H83" s="15" t="inlineStr">
-        <is>
           <t>Exploits a limited window of reduced detection around updates.</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="25.5" customHeight="1" s="9">
-      <c r="A84" s="14" t="inlineStr">
-        <is>
-          <t>A21</t>
-        </is>
-      </c>
-      <c r="B84" s="15" t="inlineStr">
-        <is>
-          <t>Update timing exploitation</t>
-        </is>
-      </c>
-      <c r="C84" s="14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D84" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F84" s="16">
-        <f>IF(D84="n/a","n/a",CHOOSE(MATCH(D84,{"Low","Medium","High"},0)*MATCH(E84,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G84" s="15" t="inlineStr">
-        <is>
-          <t>Requires knowledge of the adaptation schedule and testing data control.</t>
-        </is>
-      </c>
-      <c r="H84" s="15" t="inlineStr">
-        <is>
-          <t>Exploits a limited window of reduced detection around updates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="25.5" customHeight="1" s="9">
-      <c r="A85" s="14" t="inlineStr">
-        <is>
-          <t>A21</t>
-        </is>
-      </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>Update timing exploitation</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E85" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F85" s="16">
-        <f>IF(D85="n/a","n/a",CHOOSE(MATCH(D85,{"Low","Medium","High"},0)*MATCH(E85,{"Low","Medium","High"},0),"Note","Low","Medium","Medium","","High","","","Critical"))</f>
-        <v/>
-      </c>
-      <c r="G85" s="15" t="inlineStr">
-        <is>
-          <t>Requires knowledge of the adaptation schedule and testing data control.</t>
-        </is>
-      </c>
-      <c r="H85" s="15" t="inlineStr">
-        <is>
-          <t>Exploits a limited window of reduced detection around updates.</t>
-        </is>
-      </c>
-    </row>
+    <row r="66" ht="15" customHeight="1" s="9"/>
+    <row r="67" ht="25.5" customHeight="1" s="9"/>
+    <row r="68" ht="25.5" customHeight="1" s="9"/>
+    <row r="69" ht="25.5" customHeight="1" s="9"/>
+    <row r="70" ht="15" customHeight="1" s="9"/>
+    <row r="71" ht="25.5" customHeight="1" s="9"/>
+    <row r="72" ht="25.5" customHeight="1" s="9"/>
+    <row r="73" ht="25.5" customHeight="1" s="9"/>
+    <row r="74" ht="15" customHeight="1" s="9"/>
+    <row r="75" ht="15" customHeight="1" s="9"/>
+    <row r="76" ht="38.25" customHeight="1" s="9"/>
+    <row r="77" ht="15" customHeight="1" s="9"/>
+    <row r="78" ht="15" customHeight="1" s="9"/>
+    <row r="79" ht="25.5" customHeight="1" s="9"/>
+    <row r="80" ht="25.5" customHeight="1" s="9"/>
+    <row r="81" ht="25.5" customHeight="1" s="9"/>
+    <row r="82" ht="15" customHeight="1" s="9"/>
+    <row r="83" ht="25.5" customHeight="1" s="9"/>
+    <row r="84" ht="25.5" customHeight="1" s="9"/>
+    <row r="85" ht="25.5" customHeight="1" s="9"/>
   </sheetData>
-  <autoFilter ref="A1:H85"/>
-  <conditionalFormatting sqref="F2:F85">
+  <autoFilter ref="A1:H65"/>
+  <conditionalFormatting sqref="F2:F65">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>$F2="Note"</formula>
     </cfRule>
